--- a/data/availability/projects/sodic/sodic-east.xlsx
+++ b/data/availability/projects/sodic/sodic-east.xlsx
@@ -957,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10482,63 +10482,6 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>sodic-east</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>1</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Finished</t>
-        </is>
-      </c>
-      <c r="G157" t="n">
-        <v>0</v>
-      </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Landscape &amp; City View</t>
-        </is>
-      </c>
-      <c r="J157" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>2028-2029</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>5% down · 7–8 years equal installments</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/availability/projects/sodic/sodic-east.xlsx
+++ b/data/availability/projects/sodic/sodic-east.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Live inventory for sodic-east</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>

--- a/data/availability/projects/sodic/sodic-east.xlsx
+++ b/data/availability/projects/sodic/sodic-east.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2028-2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
